--- a/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="92">
   <si>
     <t>ORXOY</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -759,8 +760,11 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -803,21 +807,21 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3">
         <v>15300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15400</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -830,8 +834,11 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -874,21 +881,21 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
         <v>2500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2700</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -901,8 +908,11 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -945,21 +955,21 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>12700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>12800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,8 +1012,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1043,21 +1057,21 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3">
         <v>8600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1070,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,8 +1158,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1185,8 +1205,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1203,8 +1223,8 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
@@ -1212,8 +1232,11 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1256,8 +1279,8 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1274,8 +1297,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
@@ -1283,8 +1306,11 @@
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1307,8 +1333,9 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1351,21 +1378,21 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3">
         <v>22200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>19100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16700</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,8 +1405,11 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1422,21 +1452,21 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>-7000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-4800</v>
       </c>
       <c r="S18" s="3">
         <v>-4800</v>
       </c>
       <c r="T18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="U18" s="3">
         <v>-1300</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1449,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,8 +1509,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1520,21 +1554,21 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>-2400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,8 +1581,11 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1591,21 +1628,21 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-7600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,8 +1655,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1662,8 +1702,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1680,8 +1720,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1689,8 +1729,11 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1733,21 +1776,21 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3">
         <v>-9400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1500</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1760,8 +1803,11 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1804,21 +1850,21 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1831,8 +1877,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1902,8 +1951,11 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1946,21 +1998,21 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3">
         <v>-9000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2300</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1973,8 +2025,11 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2017,21 +2072,21 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3">
         <v>-9000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2300</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2044,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2115,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2159,8 +2220,8 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2177,8 +2238,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>3</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>3</v>
@@ -2186,8 +2247,11 @@
       <c r="Y29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2257,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,8 +2395,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2372,21 +2442,21 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>2400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2399,8 +2469,11 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2443,21 +2516,21 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3">
         <v>-9000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2300</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2541,8 +2617,11 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2585,21 +2664,21 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3">
         <v>-9000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2300</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,70 +2691,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2715,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2742,65 +2828,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E41" s="3">
         <v>40600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>23600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>42400</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,8 +2900,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2855,20 +2945,20 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>13200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>21500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>31000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>21600</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2884,65 +2974,68 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E43" s="3">
         <v>8100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>19000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>17700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>22800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>21200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>23700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>26700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>28500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>31900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>28800</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2955,8 +3048,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2966,54 +3062,54 @@
       <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3">
         <v>4500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3600</v>
-      </c>
-      <c r="I44" s="3">
-        <v>5400</v>
       </c>
       <c r="J44" s="3">
         <v>5400</v>
       </c>
       <c r="K44" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L44" s="3">
         <v>6500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5900</v>
-      </c>
-      <c r="O44" s="3">
-        <v>6200</v>
       </c>
       <c r="P44" s="3">
         <v>6200</v>
       </c>
       <c r="Q44" s="3">
+        <v>6200</v>
+      </c>
+      <c r="R44" s="3">
         <v>7300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7500</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,8 +3122,11 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3058,11 +3157,11 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
@@ -3070,12 +3169,12 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>3600</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3097,65 +3196,68 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E46" s="3">
         <v>50000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>126400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>39000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>40300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>40900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>44000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>48000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>45600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>47500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>52700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>56900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>72000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>79900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>85300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>78700</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,8 +3270,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3212,8 +3317,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>100</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>100</v>
@@ -3224,8 +3329,8 @@
       <c r="T47" s="3">
         <v>100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>100</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3239,65 +3344,68 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E48" s="3">
         <v>5300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8800</v>
-      </c>
-      <c r="K48" s="3">
-        <v>9300</v>
       </c>
       <c r="L48" s="3">
         <v>9300</v>
       </c>
       <c r="M48" s="3">
-        <v>10500</v>
+        <v>9300</v>
       </c>
       <c r="N48" s="3">
         <v>10500</v>
       </c>
       <c r="O48" s="3">
+        <v>10500</v>
+      </c>
+      <c r="P48" s="3">
         <v>10700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3310,65 +3418,68 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>2500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>21300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23400</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,8 +3492,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3452,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,28 +3640,31 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="E52" s="3">
         <v>6400</v>
       </c>
       <c r="F52" s="3">
-        <v>2200</v>
+        <v>6400</v>
       </c>
       <c r="G52" s="3">
         <v>2200</v>
       </c>
       <c r="H52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I52" s="3">
         <v>2100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -3562,26 +3682,26 @@
         <v>100</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2600</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3714,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3665,65 +3788,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E54" s="3">
         <v>64100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>141300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>55000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>56100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>52700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>53700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>68700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>73000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>77600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>78200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>79700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>85900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>91700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>108600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>116100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>123000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>116700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3736,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3763,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3790,56 +3920,57 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3">
         <v>8500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,52 +3992,55 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>48300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2100</v>
-      </c>
-      <c r="N58" s="3">
-        <v>2000</v>
       </c>
       <c r="O58" s="3">
         <v>2000</v>
       </c>
       <c r="P58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>2000</v>
       </c>
       <c r="R58" s="3">
         <v>2000</v>
@@ -3915,11 +4049,11 @@
         <v>2000</v>
       </c>
       <c r="T58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U58" s="3">
         <v>18600</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,65 +4066,68 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E59" s="3">
         <v>12700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>26200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>34200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>39700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14200</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,65 +4140,68 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E60" s="3">
         <v>24700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>26300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>70100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>37800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>41700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>32800</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4074,8 +4214,11 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4083,56 +4226,56 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
+        <v>300</v>
+      </c>
+      <c r="F61" s="3">
         <v>52500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>50400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>49900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>46300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>42100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>46000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>45000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>45900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>49100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>50800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>50300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>50700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>51000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4145,65 +4288,68 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E62" s="3">
         <v>800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,8 +4362,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4287,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4429,65 +4584,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E66" s="3">
         <v>25800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>88100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>78800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>76800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>68800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>65200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>71400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>70700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>71900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>72400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>71300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>74400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>79200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>89600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>87400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>93100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>84800</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4527,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4669,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4731,8 +4899,8 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-      <c r="W70" s="3" t="s">
-        <v>3</v>
+      <c r="W70" s="3">
+        <v>0</v>
       </c>
       <c r="X70" s="3" t="s">
         <v>3</v>
@@ -4740,8 +4908,11 @@
       <c r="Y70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4811,52 +4982,55 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>-147800</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-179700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>-177600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
@@ -4873,8 +5047,8 @@
       <c r="V72" s="3">
         <v>0</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -4882,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4953,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5024,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5095,65 +5278,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E76" s="3">
         <v>38300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>53200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-23800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-20700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-16100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-11400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-2700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>28800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>29900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>31900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5166,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5237,70 +5426,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5313,8 +5505,11 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5357,21 +5552,21 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3">
         <v>-9000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2300</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5384,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5411,65 +5609,66 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>1100</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3">
         <v>2100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1600</v>
-      </c>
-      <c r="O83" s="3">
-        <v>1700</v>
       </c>
       <c r="P83" s="3">
         <v>1700</v>
       </c>
       <c r="Q83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R83" s="3">
         <v>1800</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1700</v>
       </c>
       <c r="S83" s="3">
         <v>1700</v>
       </c>
       <c r="T83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U83" s="3">
         <v>1500</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5482,8 +5681,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5553,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5624,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5695,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5837,65 +6051,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>87500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
-        <v>-100</v>
-      </c>
       <c r="H89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I89" s="3">
         <v>3200</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5908,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5935,16 +6155,17 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -5961,44 +6182,44 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4500</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6006,8 +6227,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6077,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6148,16 +6375,19 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -6165,48 +6395,48 @@
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-100</v>
       </c>
       <c r="M94" s="3">
         <v>-100</v>
       </c>
       <c r="N94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>11600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>8000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>6500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-21900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6219,8 +6449,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6246,8 +6479,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6290,8 +6524,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6317,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6388,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6459,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6530,55 +6773,58 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-51900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-500</v>
       </c>
-      <c r="G100" s="3">
-        <v>500</v>
-      </c>
       <c r="H100" s="3">
+        <v>600</v>
+      </c>
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-600</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-500</v>
       </c>
       <c r="S100" s="3">
         <v>-500</v>
@@ -6586,8 +6832,8 @@
       <c r="T100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>-500</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
@@ -6601,65 +6847,68 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6672,65 +6921,68 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-55300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>87500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>10100</v>
-      </c>
-      <c r="P102" s="3">
-        <v>1000</v>
       </c>
       <c r="Q102" s="3">
         <v>1000</v>
       </c>
       <c r="R102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S102" s="3">
         <v>-11800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6400</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6741,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
